--- a/src/Excelsior.Tests/ComplexTypeWithSplitter.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ComplexTypeWithSplitter.Test.verified.xlsx
@@ -124,7 +124,7 @@
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="B2:B2">
       <formula1>ISNUMBER(B2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: SA." sqref="E2:E2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: SA." prompt="Select one of: SA." sqref="E2:E2">
       <formula1>"SA"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="F2:F2">

--- a/src/Excelsior.Tests/ComplexTypeWithSplitter.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ComplexTypeWithSplitter.Test.verified.xlsx
@@ -124,7 +124,7 @@
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="B2:B2">
       <formula1>ISNUMBER(B2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: SA." prompt="Select one of: SA." sqref="E2:E2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: SA." prompt="Select one of: SA" sqref="E2:E2">
       <formula1>"SA"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="F2:F2">

--- a/src/Excelsior.Tests/ComplexTypeWithSplitter.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ComplexTypeWithSplitter.Test.verified.xlsx
@@ -124,7 +124,7 @@
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="B2:B2">
       <formula1>ISNUMBER(B2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: SA." sqref="E2:E2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: SA." prompt="Select one of: SA" sqref="E2:E2">
       <formula1>"SA"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="F2:F2">

--- a/src/Excelsior.Tests/ComplexTypeWithSplitter.Test.verified.xlsx
+++ b/src/Excelsior.Tests/ComplexTypeWithSplitter.Test.verified.xlsx
@@ -135,7 +135,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Address.StreetNumber"/>
